--- a/pr.xlsx
+++ b/pr.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -147,8 +147,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AxTable1" displayName="AxTable1" ref="A1:R823" headerRowCount="1">
-  <autoFilter ref="A1:R823"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AxTable1" displayName="AxTable1" ref="A1:R821" headerRowCount="1">
+  <autoFilter ref="A1:R821"/>
   <tableColumns count="18">
     <tableColumn id="1" name="Purchase requisition"/>
     <tableColumn id="2" name="Quotation reference"/>
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R823"/>
+  <dimension ref="A1:R821"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -25555,7 +25555,7 @@
         </is>
       </c>
       <c r="R363" s="5" t="n">
-        <v>46190.55364583333</v>
+        <v>46273.20079861111</v>
       </c>
     </row>
     <row r="364">
@@ -37203,7 +37203,7 @@
         </is>
       </c>
       <c r="O532" t="n">
-        <v>0</v>
+        <v>2950</v>
       </c>
       <c r="P532" t="inlineStr">
         <is>
@@ -37212,11 +37212,11 @@
       </c>
       <c r="Q532" t="inlineStr">
         <is>
-          <t>Procurement sends inquiry/RFQ to suppliers</t>
+          <t>Quotation received and logged/attached</t>
         </is>
       </c>
       <c r="R532" s="5" t="n">
-        <v>46251.25571759259</v>
+        <v>46273.20859953704</v>
       </c>
     </row>
     <row r="533">
@@ -45759,7 +45759,7 @@
         </is>
       </c>
       <c r="O656" t="n">
-        <v>0</v>
+        <v>7800</v>
       </c>
       <c r="P656" t="inlineStr">
         <is>
@@ -45768,11 +45768,11 @@
       </c>
       <c r="Q656" t="inlineStr">
         <is>
-          <t>Procurement sends inquiry/RFQ to suppliers</t>
+          <t>Quotation received and logged/attached</t>
         </is>
       </c>
       <c r="R656" s="5" t="n">
-        <v>46260.22090277778</v>
+        <v>46273.224375</v>
       </c>
     </row>
     <row r="657">
@@ -48877,7 +48877,7 @@
         </is>
       </c>
       <c r="R701" s="5" t="n">
-        <v>46269.40024305556</v>
+        <v>46273.21815972222</v>
       </c>
     </row>
     <row r="702">
@@ -50865,7 +50865,7 @@
         </is>
       </c>
       <c r="O730" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="P730" t="inlineStr">
         <is>
@@ -50874,11 +50874,11 @@
       </c>
       <c r="Q730" t="inlineStr">
         <is>
-          <t>Procurement sends inquiry/RFQ to suppliers</t>
+          <t>Quotation received and logged/attached</t>
         </is>
       </c>
       <c r="R730" s="5" t="n">
-        <v>46272.3156712963</v>
+        <v>46273.23663194444</v>
       </c>
     </row>
     <row r="731">
@@ -54012,17 +54012,17 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>PR-001620</t>
+          <t>PR-001584</t>
         </is>
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Life Guard Uniform</t>
+          <t>Rectification of lifter inside office</t>
         </is>
       </c>
       <c r="D778" t="inlineStr">
         <is>
-          <t>310718</t>
+          <t>310523</t>
         </is>
       </c>
       <c r="E778" t="inlineStr">
@@ -54031,10 +54031,10 @@
         </is>
       </c>
       <c r="F778" s="5" t="n">
-        <v>46234.5</v>
+        <v>46218.5</v>
       </c>
       <c r="G778" s="5" t="n">
-        <v>46237.463125</v>
+        <v>46273.21493055556</v>
       </c>
       <c r="H778" t="inlineStr">
         <is>
@@ -54043,12 +54043,12 @@
       </c>
       <c r="K778" t="inlineStr">
         <is>
-          <t>Leisure Services</t>
+          <t>Office Support</t>
         </is>
       </c>
       <c r="L778" t="inlineStr">
         <is>
-          <t>SEVEN PALM HOTEL AND APTS</t>
+          <t>Headoffice</t>
         </is>
       </c>
       <c r="M778" t="inlineStr">
@@ -54057,36 +54057,36 @@
         </is>
       </c>
       <c r="O778" t="n">
-        <v>896</v>
+        <v>0</v>
       </c>
       <c r="P778" t="inlineStr">
         <is>
-          <t>Abdul.Muqeet</t>
+          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
         </is>
       </c>
       <c r="Q778" t="inlineStr">
         <is>
-          <t>Building Services_Asst. Facility Managers 1</t>
+          <t>Procurement sends inquiry/RFQ to suppliers</t>
         </is>
       </c>
       <c r="R778" s="5" t="n">
-        <v>46269.54230324074</v>
+        <v>46273.2152199074</v>
       </c>
     </row>
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>PR-001624</t>
+          <t>PR-001620</t>
         </is>
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>I-Rise - Supply of threshold materials July - 2026 (batch 3)</t>
+          <t>Life Guard Uniform</t>
         </is>
       </c>
       <c r="D779" t="inlineStr">
         <is>
-          <t>310523</t>
+          <t>310718</t>
         </is>
       </c>
       <c r="E779" t="inlineStr">
@@ -54095,10 +54095,10 @@
         </is>
       </c>
       <c r="F779" s="5" t="n">
-        <v>46237.5</v>
+        <v>46234.5</v>
       </c>
       <c r="G779" s="5" t="n">
-        <v>46237.31061342593</v>
+        <v>46237.463125</v>
       </c>
       <c r="H779" t="inlineStr">
         <is>
@@ -54107,12 +54107,12 @@
       </c>
       <c r="K779" t="inlineStr">
         <is>
-          <t>Building Services</t>
+          <t>Leisure Services</t>
         </is>
       </c>
       <c r="L779" t="inlineStr">
         <is>
-          <t>I RISE TOWER</t>
+          <t>SEVEN PALM HOTEL AND APTS</t>
         </is>
       </c>
       <c r="M779" t="inlineStr">
@@ -54121,31 +54121,31 @@
         </is>
       </c>
       <c r="O779" t="n">
-        <v>0</v>
+        <v>896</v>
       </c>
       <c r="P779" t="inlineStr">
         <is>
-          <t>Adnan.Ullah</t>
+          <t>Abdul.Muqeet</t>
         </is>
       </c>
       <c r="Q779" t="inlineStr">
         <is>
-          <t>Procurement sends inquiry/RFQ to suppliers</t>
+          <t>Building Services_Asst. Facility Managers 1</t>
         </is>
       </c>
       <c r="R779" s="5" t="n">
-        <v>46258.35056712963</v>
+        <v>46269.54230324074</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>PR-001643</t>
+          <t>PR-001624</t>
         </is>
       </c>
       <c r="C780" t="inlineStr">
         <is>
-          <t>MEP Consumable materials Aug-26</t>
+          <t>I-Rise - Supply of threshold materials July - 2026 (batch 3)</t>
         </is>
       </c>
       <c r="D780" t="inlineStr">
@@ -54159,10 +54159,10 @@
         </is>
       </c>
       <c r="F780" s="5" t="n">
-        <v>46242.5</v>
+        <v>46237.5</v>
       </c>
       <c r="G780" s="5" t="n">
-        <v>46242.3646875</v>
+        <v>46237.31061342593</v>
       </c>
       <c r="H780" t="inlineStr">
         <is>
@@ -54176,7 +54176,7 @@
       </c>
       <c r="L780" t="inlineStr">
         <is>
-          <t>BELGRAVIA SQUARE JVC</t>
+          <t>I RISE TOWER</t>
         </is>
       </c>
       <c r="M780" t="inlineStr">
@@ -54198,18 +54198,18 @@
         </is>
       </c>
       <c r="R780" s="5" t="n">
-        <v>46248.23214120371</v>
+        <v>46258.35056712963</v>
       </c>
     </row>
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>PR-001649</t>
+          <t>PR-001643</t>
         </is>
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Head Office Additional Chairs in the Pantry</t>
+          <t>MEP Consumable materials Aug-26</t>
         </is>
       </c>
       <c r="D781" t="inlineStr">
@@ -54223,10 +54223,10 @@
         </is>
       </c>
       <c r="F781" s="5" t="n">
-        <v>46244.5</v>
+        <v>46242.5</v>
       </c>
       <c r="G781" s="5" t="n">
-        <v>46244.49505787037</v>
+        <v>46242.3646875</v>
       </c>
       <c r="H781" t="inlineStr">
         <is>
@@ -54235,12 +54235,12 @@
       </c>
       <c r="K781" t="inlineStr">
         <is>
-          <t>Office Support</t>
+          <t>Building Services</t>
         </is>
       </c>
       <c r="L781" t="inlineStr">
         <is>
-          <t>Headoffice</t>
+          <t>BELGRAVIA SQUARE JVC</t>
         </is>
       </c>
       <c r="M781" t="inlineStr">
@@ -54253,7 +54253,7 @@
       </c>
       <c r="P781" t="inlineStr">
         <is>
-          <t>Aparna.Pauly</t>
+          <t>Adnan.Ullah</t>
         </is>
       </c>
       <c r="Q781" t="inlineStr">
@@ -54262,18 +54262,18 @@
         </is>
       </c>
       <c r="R781" s="5" t="n">
-        <v>46260.25315972222</v>
+        <v>46248.23214120371</v>
       </c>
     </row>
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>PR-001654</t>
+          <t>PR-001649</t>
         </is>
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Supply of consumable materials</t>
+          <t>Head Office Additional Chairs in the Pantry</t>
         </is>
       </c>
       <c r="D782" t="inlineStr">
@@ -54287,10 +54287,10 @@
         </is>
       </c>
       <c r="F782" s="5" t="n">
-        <v>46245.5</v>
+        <v>46244.5</v>
       </c>
       <c r="G782" s="5" t="n">
-        <v>46246.22689814815</v>
+        <v>46244.49505787037</v>
       </c>
       <c r="H782" t="inlineStr">
         <is>
@@ -54299,12 +54299,12 @@
       </c>
       <c r="K782" t="inlineStr">
         <is>
-          <t>Building Services</t>
+          <t>Office Support</t>
         </is>
       </c>
       <c r="L782" t="inlineStr">
         <is>
-          <t>NORTH RESIDENCE</t>
+          <t>Headoffice</t>
         </is>
       </c>
       <c r="M782" t="inlineStr">
@@ -54313,11 +54313,11 @@
         </is>
       </c>
       <c r="O782" t="n">
-        <v>2412</v>
+        <v>0</v>
       </c>
       <c r="P782" t="inlineStr">
         <is>
-          <t>arman.b</t>
+          <t>Aparna.Pauly</t>
         </is>
       </c>
       <c r="Q782" t="inlineStr">
@@ -54326,18 +54326,18 @@
         </is>
       </c>
       <c r="R782" s="5" t="n">
-        <v>46272.45961805555</v>
+        <v>46260.25315972222</v>
       </c>
     </row>
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>PR-001661</t>
+          <t>PR-001654</t>
         </is>
       </c>
       <c r="C783" t="inlineStr">
         <is>
-          <t>MAG 318 -RFP Supply of Consumables material</t>
+          <t>Supply of consumable materials</t>
         </is>
       </c>
       <c r="D783" t="inlineStr">
@@ -54351,10 +54351,10 @@
         </is>
       </c>
       <c r="F783" s="5" t="n">
-        <v>46246.5</v>
+        <v>46245.5</v>
       </c>
       <c r="G783" s="5" t="n">
-        <v>46246.44836805556</v>
+        <v>46246.22689814815</v>
       </c>
       <c r="H783" t="inlineStr">
         <is>
@@ -54368,7 +54368,7 @@
       </c>
       <c r="L783" t="inlineStr">
         <is>
-          <t>MAG 318</t>
+          <t>NORTH RESIDENCE</t>
         </is>
       </c>
       <c r="M783" t="inlineStr">
@@ -54377,11 +54377,11 @@
         </is>
       </c>
       <c r="O783" t="n">
-        <v>0</v>
+        <v>2412</v>
       </c>
       <c r="P783" t="inlineStr">
         <is>
-          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
+          <t>arman.b</t>
         </is>
       </c>
       <c r="Q783" t="inlineStr">
@@ -54390,18 +54390,18 @@
         </is>
       </c>
       <c r="R783" s="5" t="n">
-        <v>46255.31451388889</v>
+        <v>46272.45961805555</v>
       </c>
     </row>
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>PR-001662</t>
+          <t>PR-001661</t>
         </is>
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>BELGRAVIA - MEP Consumable materials Aug-26</t>
+          <t>MAG 318 -RFP Supply of Consumables material</t>
         </is>
       </c>
       <c r="D784" t="inlineStr">
@@ -54418,7 +54418,7 @@
         <v>46246.5</v>
       </c>
       <c r="G784" s="5" t="n">
-        <v>46246.51336805556</v>
+        <v>46246.44836805556</v>
       </c>
       <c r="H784" t="inlineStr">
         <is>
@@ -54432,7 +54432,7 @@
       </c>
       <c r="L784" t="inlineStr">
         <is>
-          <t>BELGRAVIA SQUARE JVC</t>
+          <t>MAG 318</t>
         </is>
       </c>
       <c r="M784" t="inlineStr">
@@ -54445,7 +54445,7 @@
       </c>
       <c r="P784" t="inlineStr">
         <is>
-          <t>Adnan.Ullah</t>
+          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
         </is>
       </c>
       <c r="Q784" t="inlineStr">
@@ -54454,23 +54454,23 @@
         </is>
       </c>
       <c r="R784" s="5" t="n">
-        <v>46247.35737268518</v>
+        <v>46255.31451388889</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>PR-001678</t>
+          <t>PR-001662</t>
         </is>
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Supply of Coco Brush</t>
+          <t>BELGRAVIA - MEP Consumable materials Aug-26</t>
         </is>
       </c>
       <c r="D785" t="inlineStr">
         <is>
-          <t>312005</t>
+          <t>310523</t>
         </is>
       </c>
       <c r="E785" t="inlineStr">
@@ -54479,10 +54479,10 @@
         </is>
       </c>
       <c r="F785" s="5" t="n">
-        <v>46251.5</v>
+        <v>46246.5</v>
       </c>
       <c r="G785" s="5" t="n">
-        <v>46255.27901620371</v>
+        <v>46246.51336805556</v>
       </c>
       <c r="H785" t="inlineStr">
         <is>
@@ -54491,12 +54491,12 @@
       </c>
       <c r="K785" t="inlineStr">
         <is>
-          <t>Contracted Cleaning Services</t>
+          <t>Building Services</t>
         </is>
       </c>
       <c r="L785" t="inlineStr">
         <is>
-          <t>J ONE TOWER</t>
+          <t>BELGRAVIA SQUARE JVC</t>
         </is>
       </c>
       <c r="M785" t="inlineStr">
@@ -54518,18 +54518,18 @@
         </is>
       </c>
       <c r="R785" s="5" t="n">
-        <v>46259.4784375</v>
+        <v>46247.35737268518</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>PR-001679</t>
+          <t>PR-001678</t>
         </is>
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>PAC-Magic Sponge</t>
+          <t>Supply of Coco Brush</t>
         </is>
       </c>
       <c r="D786" t="inlineStr">
@@ -54546,7 +54546,7 @@
         <v>46251.5</v>
       </c>
       <c r="G786" s="5" t="n">
-        <v>46252.23553240741</v>
+        <v>46255.27901620371</v>
       </c>
       <c r="H786" t="inlineStr">
         <is>
@@ -54582,23 +54582,23 @@
         </is>
       </c>
       <c r="R786" s="5" t="n">
-        <v>46258.34215277778</v>
+        <v>46259.4784375</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>PR-001682</t>
+          <t>PR-001679</t>
         </is>
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Uniform for Head Office Security Team</t>
+          <t>PAC-Magic Sponge</t>
         </is>
       </c>
       <c r="D787" t="inlineStr">
         <is>
-          <t>310718</t>
+          <t>312005</t>
         </is>
       </c>
       <c r="E787" t="inlineStr">
@@ -54607,10 +54607,10 @@
         </is>
       </c>
       <c r="F787" s="5" t="n">
-        <v>46252.5</v>
+        <v>46251.5</v>
       </c>
       <c r="G787" s="5" t="n">
-        <v>46261.25381944444</v>
+        <v>46252.23553240741</v>
       </c>
       <c r="H787" t="inlineStr">
         <is>
@@ -54619,12 +54619,12 @@
       </c>
       <c r="K787" t="inlineStr">
         <is>
-          <t>Security Services</t>
+          <t>Contracted Cleaning Services</t>
         </is>
       </c>
       <c r="L787" t="inlineStr">
         <is>
-          <t>Headoffice</t>
+          <t>J ONE TOWER</t>
         </is>
       </c>
       <c r="M787" t="inlineStr">
@@ -54633,36 +54633,36 @@
         </is>
       </c>
       <c r="O787" t="n">
-        <v>795</v>
+        <v>0</v>
       </c>
       <c r="P787" t="inlineStr">
         <is>
-          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
+          <t>Adnan.Ullah</t>
         </is>
       </c>
       <c r="Q787" t="inlineStr">
         <is>
-          <t>Quotation received and logged/attached</t>
+          <t>Procurement sends inquiry/RFQ to suppliers</t>
         </is>
       </c>
       <c r="R787" s="5" t="n">
-        <v>46261.25407407407</v>
+        <v>46258.34215277778</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>PR-001684</t>
+          <t>PR-001682</t>
         </is>
       </c>
       <c r="C788" t="inlineStr">
         <is>
-          <t>New Wet &amp; Dry Machine</t>
+          <t>Uniform for Head Office Security Team</t>
         </is>
       </c>
       <c r="D788" t="inlineStr">
         <is>
-          <t>312005</t>
+          <t>310718</t>
         </is>
       </c>
       <c r="E788" t="inlineStr">
@@ -54674,7 +54674,7 @@
         <v>46252.5</v>
       </c>
       <c r="G788" s="5" t="n">
-        <v>46267.40340277777</v>
+        <v>46261.25381944444</v>
       </c>
       <c r="H788" t="inlineStr">
         <is>
@@ -54683,12 +54683,12 @@
       </c>
       <c r="K788" t="inlineStr">
         <is>
-          <t>Contracted Cleaning Services</t>
+          <t>Security Services</t>
         </is>
       </c>
       <c r="L788" t="inlineStr">
         <is>
-          <t>IRIS BLUE</t>
+          <t>Headoffice</t>
         </is>
       </c>
       <c r="M788" t="inlineStr">
@@ -54697,11 +54697,11 @@
         </is>
       </c>
       <c r="O788" t="n">
-        <v>1300</v>
+        <v>795</v>
       </c>
       <c r="P788" t="inlineStr">
         <is>
-          <t>arman.b</t>
+          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
         </is>
       </c>
       <c r="Q788" t="inlineStr">
@@ -54710,7 +54710,7 @@
         </is>
       </c>
       <c r="R788" s="5" t="n">
-        <v>46269.5428587963</v>
+        <v>46261.25407407407</v>
       </c>
     </row>
     <row r="789">
@@ -55932,17 +55932,17 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>PR-001743</t>
+          <t>PR-001744</t>
         </is>
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Arbor School First Aid Kit</t>
+          <t>The Binary  High pressure Machine Reapir</t>
         </is>
       </c>
       <c r="D808" t="inlineStr">
         <is>
-          <t>310523</t>
+          <t>312005</t>
         </is>
       </c>
       <c r="E808" t="inlineStr">
@@ -55954,7 +55954,7 @@
         <v>46266.5</v>
       </c>
       <c r="G808" s="5" t="n">
-        <v>46266.46877314815</v>
+        <v>46266.53716435185</v>
       </c>
       <c r="H808" t="inlineStr">
         <is>
@@ -55963,12 +55963,12 @@
       </c>
       <c r="K808" t="inlineStr">
         <is>
-          <t>Building Services</t>
+          <t>Contracted Cleaning Services</t>
         </is>
       </c>
       <c r="L808" t="inlineStr">
         <is>
-          <t>ARBOR SCHOOL</t>
+          <t>THE BINARY BY OMNIYAT</t>
         </is>
       </c>
       <c r="M808" t="inlineStr">
@@ -55977,36 +55977,36 @@
         </is>
       </c>
       <c r="O808" t="n">
-        <v>435</v>
+        <v>0</v>
       </c>
       <c r="P808" t="inlineStr">
         <is>
-          <t>arman.b</t>
+          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
         </is>
       </c>
       <c r="Q808" t="inlineStr">
         <is>
-          <t>Quotation received and logged/attached</t>
+          <t>Procurement sends inquiry/RFQ to suppliers</t>
         </is>
       </c>
       <c r="R808" s="5" t="n">
-        <v>46272.45892361111</v>
+        <v>46269.27982638889</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>PR-001744</t>
+          <t>PR-001746</t>
         </is>
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>The Binary  High pressure Machine Reapir</t>
+          <t>The Binary - Supply of MEP materials of Sep 26</t>
         </is>
       </c>
       <c r="D809" t="inlineStr">
         <is>
-          <t>312005</t>
+          <t>310523</t>
         </is>
       </c>
       <c r="E809" t="inlineStr">
@@ -56015,10 +56015,10 @@
         </is>
       </c>
       <c r="F809" s="5" t="n">
-        <v>46266.5</v>
+        <v>46267.5</v>
       </c>
       <c r="G809" s="5" t="n">
-        <v>46266.53716435185</v>
+        <v>46267.3153125</v>
       </c>
       <c r="H809" t="inlineStr">
         <is>
@@ -56027,7 +56027,7 @@
       </c>
       <c r="K809" t="inlineStr">
         <is>
-          <t>Contracted Cleaning Services</t>
+          <t>Building Services</t>
         </is>
       </c>
       <c r="L809" t="inlineStr">
@@ -56045,7 +56045,7 @@
       </c>
       <c r="P809" t="inlineStr">
         <is>
-          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
+          <t>Adnan.Ullah</t>
         </is>
       </c>
       <c r="Q809" t="inlineStr">
@@ -56054,23 +56054,23 @@
         </is>
       </c>
       <c r="R809" s="5" t="n">
-        <v>46269.27982638889</v>
+        <v>46269.52929398148</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>PR-001746</t>
+          <t>PR-001747</t>
         </is>
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>The Binary - Supply of MEP materials of Sep 26</t>
+          <t>Iris Blue -New Single disc machine</t>
         </is>
       </c>
       <c r="D810" t="inlineStr">
         <is>
-          <t>310523</t>
+          <t>312005</t>
         </is>
       </c>
       <c r="E810" t="inlineStr">
@@ -56082,7 +56082,7 @@
         <v>46267.5</v>
       </c>
       <c r="G810" s="5" t="n">
-        <v>46267.3153125</v>
+        <v>46272.51527777778</v>
       </c>
       <c r="H810" t="inlineStr">
         <is>
@@ -56091,12 +56091,12 @@
       </c>
       <c r="K810" t="inlineStr">
         <is>
-          <t>Building Services</t>
+          <t>Contracted Cleaning Services</t>
         </is>
       </c>
       <c r="L810" t="inlineStr">
         <is>
-          <t>THE BINARY BY OMNIYAT</t>
+          <t>IRIS BLUE</t>
         </is>
       </c>
       <c r="M810" t="inlineStr">
@@ -56109,7 +56109,7 @@
       </c>
       <c r="P810" t="inlineStr">
         <is>
-          <t>Adnan.Ullah</t>
+          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
         </is>
       </c>
       <c r="Q810" t="inlineStr">
@@ -56118,23 +56118,23 @@
         </is>
       </c>
       <c r="R810" s="5" t="n">
-        <v>46269.52929398148</v>
+        <v>46272.51582175926</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>PR-001747</t>
+          <t>PR-001748</t>
         </is>
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Iris Blue -New Single disc machine</t>
+          <t>Bayswater - Supply of MEP materials of Sep 26</t>
         </is>
       </c>
       <c r="D811" t="inlineStr">
         <is>
-          <t>312005</t>
+          <t>310523</t>
         </is>
       </c>
       <c r="E811" t="inlineStr">
@@ -56146,7 +56146,7 @@
         <v>46267.5</v>
       </c>
       <c r="G811" s="5" t="n">
-        <v>46272.51527777778</v>
+        <v>46267.34322916667</v>
       </c>
       <c r="H811" t="inlineStr">
         <is>
@@ -56155,12 +56155,12 @@
       </c>
       <c r="K811" t="inlineStr">
         <is>
-          <t>Contracted Cleaning Services</t>
+          <t>Building Services</t>
         </is>
       </c>
       <c r="L811" t="inlineStr">
         <is>
-          <t>IRIS BLUE</t>
+          <t>THE BAYSWATER BY OMNIYAT</t>
         </is>
       </c>
       <c r="M811" t="inlineStr">
@@ -56173,7 +56173,7 @@
       </c>
       <c r="P811" t="inlineStr">
         <is>
-          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
+          <t>Adnan.Ullah</t>
         </is>
       </c>
       <c r="Q811" t="inlineStr">
@@ -56182,23 +56182,23 @@
         </is>
       </c>
       <c r="R811" s="5" t="n">
-        <v>46272.51582175926</v>
+        <v>46272.1999074074</v>
       </c>
     </row>
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>PR-001748</t>
+          <t>PR-001750</t>
         </is>
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Bayswater - Supply of MEP materials of Sep 26</t>
+          <t>Monreve Single disc machine repair</t>
         </is>
       </c>
       <c r="D812" t="inlineStr">
         <is>
-          <t>310523</t>
+          <t>312005</t>
         </is>
       </c>
       <c r="E812" t="inlineStr">
@@ -56210,7 +56210,7 @@
         <v>46267.5</v>
       </c>
       <c r="G812" s="5" t="n">
-        <v>46267.34322916667</v>
+        <v>46267.38841435185</v>
       </c>
       <c r="H812" t="inlineStr">
         <is>
@@ -56219,12 +56219,12 @@
       </c>
       <c r="K812" t="inlineStr">
         <is>
-          <t>Building Services</t>
+          <t>Contracted Cleaning Services</t>
         </is>
       </c>
       <c r="L812" t="inlineStr">
         <is>
-          <t>THE BAYSWATER BY OMNIYAT</t>
+          <t>MONREVE TOWER</t>
         </is>
       </c>
       <c r="M812" t="inlineStr">
@@ -56237,7 +56237,7 @@
       </c>
       <c r="P812" t="inlineStr">
         <is>
-          <t>Adnan.Ullah</t>
+          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
         </is>
       </c>
       <c r="Q812" t="inlineStr">
@@ -56246,18 +56246,18 @@
         </is>
       </c>
       <c r="R812" s="5" t="n">
-        <v>46272.1999074074</v>
+        <v>46267.38884259259</v>
       </c>
     </row>
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>PR-001750</t>
+          <t>PR-001751</t>
         </is>
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Monreve Single disc machine repair</t>
+          <t>Wilton park single disc machine replace</t>
         </is>
       </c>
       <c r="D813" t="inlineStr">
@@ -56274,7 +56274,7 @@
         <v>46267.5</v>
       </c>
       <c r="G813" s="5" t="n">
-        <v>46267.38841435185</v>
+        <v>46267.44914351852</v>
       </c>
       <c r="H813" t="inlineStr">
         <is>
@@ -56288,7 +56288,7 @@
       </c>
       <c r="L813" t="inlineStr">
         <is>
-          <t>MONREVE TOWER</t>
+          <t>WILTON PARK RESIDENCES</t>
         </is>
       </c>
       <c r="M813" t="inlineStr">
@@ -56310,18 +56310,18 @@
         </is>
       </c>
       <c r="R813" s="5" t="n">
-        <v>46267.38884259259</v>
+        <v>46267.44925925926</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>PR-001751</t>
+          <t>PR-001753</t>
         </is>
       </c>
       <c r="C814" t="inlineStr">
         <is>
-          <t>Wilton park single disc machine replace</t>
+          <t>One by Omniyat High Pressure machine repair</t>
         </is>
       </c>
       <c r="D814" t="inlineStr">
@@ -56338,7 +56338,7 @@
         <v>46267.5</v>
       </c>
       <c r="G814" s="5" t="n">
-        <v>46267.44914351852</v>
+        <v>46267.48268518518</v>
       </c>
       <c r="H814" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
       </c>
       <c r="L814" t="inlineStr">
         <is>
-          <t>WILTON PARK RESIDENCES</t>
+          <t>ONE BY OMNIYAT</t>
         </is>
       </c>
       <c r="M814" t="inlineStr">
@@ -56374,18 +56374,18 @@
         </is>
       </c>
       <c r="R814" s="5" t="n">
-        <v>46267.44925925926</v>
+        <v>46267.48324074074</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>PR-001753</t>
+          <t>PR-001754</t>
         </is>
       </c>
       <c r="C815" t="inlineStr">
         <is>
-          <t>One by Omniyat High Pressure machine repair</t>
+          <t>PAC Pad holder replace-Al Maaref</t>
         </is>
       </c>
       <c r="D815" t="inlineStr">
@@ -56402,7 +56402,7 @@
         <v>46267.5</v>
       </c>
       <c r="G815" s="5" t="n">
-        <v>46267.48268518518</v>
+        <v>46267.4887037037</v>
       </c>
       <c r="H815" t="inlineStr">
         <is>
@@ -56416,7 +56416,7 @@
       </c>
       <c r="L815" t="inlineStr">
         <is>
-          <t>ONE BY OMNIYAT</t>
+          <t>AL MAAREF PRIVATE SCHOOL</t>
         </is>
       </c>
       <c r="M815" t="inlineStr">
@@ -56438,23 +56438,23 @@
         </is>
       </c>
       <c r="R815" s="5" t="n">
-        <v>46267.48324074074</v>
+        <v>46267.48944444444</v>
       </c>
     </row>
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>PR-001754</t>
+          <t>PR-001759</t>
         </is>
       </c>
       <c r="C816" t="inlineStr">
         <is>
-          <t>PAC Pad holder replace-Al Maaref</t>
+          <t>J ONE supply Of First Aid Kit Box 25person</t>
         </is>
       </c>
       <c r="D816" t="inlineStr">
         <is>
-          <t>312005</t>
+          <t>310523</t>
         </is>
       </c>
       <c r="E816" t="inlineStr">
@@ -56463,10 +56463,10 @@
         </is>
       </c>
       <c r="F816" s="5" t="n">
-        <v>46267.5</v>
+        <v>46269.5</v>
       </c>
       <c r="G816" s="5" t="n">
-        <v>46267.4887037037</v>
+        <v>46269.27866898148</v>
       </c>
       <c r="H816" t="inlineStr">
         <is>
@@ -56475,12 +56475,12 @@
       </c>
       <c r="K816" t="inlineStr">
         <is>
-          <t>Contracted Cleaning Services</t>
+          <t>Building Services</t>
         </is>
       </c>
       <c r="L816" t="inlineStr">
         <is>
-          <t>AL MAAREF PRIVATE SCHOOL</t>
+          <t>J ONE TOWER</t>
         </is>
       </c>
       <c r="M816" t="inlineStr">
@@ -56493,32 +56493,32 @@
       </c>
       <c r="P816" t="inlineStr">
         <is>
-          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
+          <t>ruben.senesan</t>
         </is>
       </c>
       <c r="Q816" t="inlineStr">
         <is>
-          <t>Procurement sends inquiry/RFQ to suppliers</t>
+          <t>Building Services_Asst. Facility Managers 1</t>
         </is>
       </c>
       <c r="R816" s="5" t="n">
-        <v>46267.48944444444</v>
+        <v>46269.28101851852</v>
       </c>
     </row>
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>PR-001758</t>
+          <t>PR-001761</t>
         </is>
       </c>
       <c r="C817" t="inlineStr">
         <is>
-          <t>Flush Tanks Mechanism</t>
+          <t>PAC- Cleaning tools -Zone 1</t>
         </is>
       </c>
       <c r="D817" t="inlineStr">
         <is>
-          <t>311141</t>
+          <t>312005</t>
         </is>
       </c>
       <c r="E817" t="inlineStr">
@@ -56527,10 +56527,10 @@
         </is>
       </c>
       <c r="F817" s="5" t="n">
-        <v>46268.5</v>
+        <v>46269.5</v>
       </c>
       <c r="G817" s="5" t="n">
-        <v>46268.58456018518</v>
+        <v>46269.4728125</v>
       </c>
       <c r="H817" t="inlineStr">
         <is>
@@ -56539,12 +56539,12 @@
       </c>
       <c r="K817" t="inlineStr">
         <is>
-          <t>Accomodation Services</t>
+          <t>Contracted Cleaning Services</t>
         </is>
       </c>
       <c r="L817" t="inlineStr">
         <is>
-          <t>AL RAMS LABOUR CAMP 1</t>
+          <t>BEACH WALK 1 BY IMTIAZ</t>
         </is>
       </c>
       <c r="M817" t="inlineStr">
@@ -56553,31 +56553,31 @@
         </is>
       </c>
       <c r="O817" t="n">
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="P817" t="inlineStr">
         <is>
-          <t>arman.b</t>
+          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
         </is>
       </c>
       <c r="Q817" t="inlineStr">
         <is>
-          <t>Finance &amp; Accounts_Accounting Manager</t>
+          <t>Procurement sends inquiry/RFQ to suppliers</t>
         </is>
       </c>
       <c r="R817" s="5" t="n">
-        <v>46269.32913194445</v>
+        <v>46269.47354166667</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>PR-001759</t>
+          <t>PR-001762</t>
         </is>
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>J ONE supply Of First Aid Kit Box 25person</t>
+          <t>Prism Tower - Supply of Monthly Consumables -SEP- 2026</t>
         </is>
       </c>
       <c r="D818" t="inlineStr">
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="F818" s="5" t="n">
-        <v>46269.5</v>
+        <v>46272.5</v>
       </c>
       <c r="G818" s="5" t="n">
-        <v>46269.27866898148</v>
+        <v>46272.24703703704</v>
       </c>
       <c r="H818" t="inlineStr">
         <is>
@@ -56608,7 +56608,7 @@
       </c>
       <c r="L818" t="inlineStr">
         <is>
-          <t>J ONE TOWER</t>
+          <t>THE PRISM TOWER</t>
         </is>
       </c>
       <c r="M818" t="inlineStr">
@@ -56621,32 +56621,32 @@
       </c>
       <c r="P818" t="inlineStr">
         <is>
-          <t>ruben.senesan</t>
+          <t>Adnan.Ullah</t>
         </is>
       </c>
       <c r="Q818" t="inlineStr">
         <is>
-          <t>Building Services_Asst. Facility Managers 1</t>
+          <t>Procurement sends inquiry/RFQ to suppliers</t>
         </is>
       </c>
       <c r="R818" s="5" t="n">
-        <v>46269.28101851852</v>
+        <v>46272.55219907407</v>
       </c>
     </row>
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>PR-001761</t>
+          <t>PR-001763</t>
         </is>
       </c>
       <c r="C819" t="inlineStr">
         <is>
-          <t>PAC- Cleaning tools -Zone 1</t>
+          <t>J One Consumable Items Sep 2026</t>
         </is>
       </c>
       <c r="D819" t="inlineStr">
         <is>
-          <t>312005</t>
+          <t>310523</t>
         </is>
       </c>
       <c r="E819" t="inlineStr">
@@ -56655,10 +56655,10 @@
         </is>
       </c>
       <c r="F819" s="5" t="n">
-        <v>46269.5</v>
+        <v>46272.5</v>
       </c>
       <c r="G819" s="5" t="n">
-        <v>46269.4728125</v>
+        <v>46272.23798611111</v>
       </c>
       <c r="H819" t="inlineStr">
         <is>
@@ -56667,12 +56667,12 @@
       </c>
       <c r="K819" t="inlineStr">
         <is>
-          <t>Contracted Cleaning Services</t>
+          <t>Building Services</t>
         </is>
       </c>
       <c r="L819" t="inlineStr">
         <is>
-          <t>BEACH WALK 1 BY IMTIAZ</t>
+          <t>J ONE TOWER</t>
         </is>
       </c>
       <c r="M819" t="inlineStr">
@@ -56694,18 +56694,18 @@
         </is>
       </c>
       <c r="R819" s="5" t="n">
-        <v>46269.47354166667</v>
+        <v>46272.37555555555</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>PR-001762</t>
+          <t>PR-001765</t>
         </is>
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Prism Tower - Supply of Monthly Consumables -SEP- 2026</t>
+          <t xml:space="preserve"> The Autograph-Tools</t>
         </is>
       </c>
       <c r="D820" t="inlineStr">
@@ -56722,7 +56722,7 @@
         <v>46272.5</v>
       </c>
       <c r="G820" s="5" t="n">
-        <v>46272.24703703704</v>
+        <v>46272.52758101852</v>
       </c>
       <c r="H820" t="inlineStr">
         <is>
@@ -56736,7 +56736,7 @@
       </c>
       <c r="L820" t="inlineStr">
         <is>
-          <t>THE PRISM TOWER</t>
+          <t>THE AUTOGRAPH</t>
         </is>
       </c>
       <c r="M820" t="inlineStr">
@@ -56749,7 +56749,7 @@
       </c>
       <c r="P820" t="inlineStr">
         <is>
-          <t>Adnan.Ullah</t>
+          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
         </is>
       </c>
       <c r="Q820" t="inlineStr">
@@ -56758,18 +56758,18 @@
         </is>
       </c>
       <c r="R820" s="5" t="n">
-        <v>46272.55219907407</v>
+        <v>46272.52774305556</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>PR-001763</t>
+          <t>PR-001766</t>
         </is>
       </c>
       <c r="C821" t="inlineStr">
         <is>
-          <t>J One Consumable Items Sep 2026</t>
+          <t>Residence 110 Submission of RFQ – Common Area Three-Month Co</t>
         </is>
       </c>
       <c r="D821" t="inlineStr">
@@ -56786,7 +56786,7 @@
         <v>46272.5</v>
       </c>
       <c r="G821" s="5" t="n">
-        <v>46272.23798611111</v>
+        <v>46272.56884259259</v>
       </c>
       <c r="H821" t="inlineStr">
         <is>
@@ -56800,7 +56800,7 @@
       </c>
       <c r="L821" t="inlineStr">
         <is>
-          <t>J ONE TOWER</t>
+          <t>RESIDENCE 110</t>
         </is>
       </c>
       <c r="M821" t="inlineStr">
@@ -56822,135 +56822,7 @@
         </is>
       </c>
       <c r="R821" s="5" t="n">
-        <v>46272.37555555555</v>
-      </c>
-    </row>
-    <row r="822">
-      <c r="A822" t="inlineStr">
-        <is>
-          <t>PR-001765</t>
-        </is>
-      </c>
-      <c r="C822" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> The Autograph-Tools</t>
-        </is>
-      </c>
-      <c r="D822" t="inlineStr">
-        <is>
-          <t>310523</t>
-        </is>
-      </c>
-      <c r="E822" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="F822" s="5" t="n">
-        <v>46272.5</v>
-      </c>
-      <c r="G822" s="5" t="n">
-        <v>46272.52758101852</v>
-      </c>
-      <c r="H822" t="inlineStr">
-        <is>
-          <t>Consumption</t>
-        </is>
-      </c>
-      <c r="K822" t="inlineStr">
-        <is>
-          <t>Building Services</t>
-        </is>
-      </c>
-      <c r="L822" t="inlineStr">
-        <is>
-          <t>THE AUTOGRAPH</t>
-        </is>
-      </c>
-      <c r="M822" t="inlineStr">
-        <is>
-          <t>Contracted</t>
-        </is>
-      </c>
-      <c r="O822" t="n">
-        <v>0</v>
-      </c>
-      <c r="P822" t="inlineStr">
-        <is>
-          <t>Adnan.Ullah, Aparna.Pauly, Layusha.cleatus, roderick.red</t>
-        </is>
-      </c>
-      <c r="Q822" t="inlineStr">
-        <is>
-          <t>Procurement sends inquiry/RFQ to suppliers</t>
-        </is>
-      </c>
-      <c r="R822" s="5" t="n">
-        <v>46272.52774305556</v>
-      </c>
-    </row>
-    <row r="823">
-      <c r="A823" t="inlineStr">
-        <is>
-          <t>PR-001766</t>
-        </is>
-      </c>
-      <c r="C823" t="inlineStr">
-        <is>
-          <t>Residence 110 Submission of RFQ – Common Area Three-Month Co</t>
-        </is>
-      </c>
-      <c r="D823" t="inlineStr">
-        <is>
-          <t>310523</t>
-        </is>
-      </c>
-      <c r="E823" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="F823" s="5" t="n">
-        <v>46272.5</v>
-      </c>
-      <c r="G823" s="5" t="n">
-        <v>46272.56884259259</v>
-      </c>
-      <c r="H823" t="inlineStr">
-        <is>
-          <t>Consumption</t>
-        </is>
-      </c>
-      <c r="K823" t="inlineStr">
-        <is>
-          <t>Building Services</t>
-        </is>
-      </c>
-      <c r="L823" t="inlineStr">
-        <is>
-          <t>RESIDENCE 110</t>
-        </is>
-      </c>
-      <c r="M823" t="inlineStr">
-        <is>
-          <t>Contracted</t>
-        </is>
-      </c>
-      <c r="O823" t="n">
-        <v>0</v>
-      </c>
-      <c r="P823" t="inlineStr">
-        <is>
-          <t>ruben.senesan</t>
-        </is>
-      </c>
-      <c r="Q823" t="inlineStr">
-        <is>
-          <t>Building Services_Asst. Facility Managers 1</t>
-        </is>
-      </c>
-      <c r="R823" s="5" t="n">
-        <v>46272.57112268519</v>
+        <v>46273.17564814815</v>
       </c>
     </row>
   </sheetData>
